--- a/output/pdf_financials_xlsx/SIA.xlsx
+++ b/output/pdf_financials_xlsx/SIA.xlsx
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>15.623</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>29.033</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>15.623</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>29.033</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>44.372</v>
+        <v>28.749</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>51.848</v>
+        <v>22.815</v>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
@@ -7165,7 +7165,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">

--- a/output/pdf_financials_xlsx/SIA.xlsx
+++ b/output/pdf_financials_xlsx/SIA.xlsx
@@ -3475,25 +3475,25 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>28.845</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>39.511</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>34.588</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>39.646</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>37.62</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>71.17400000000001</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>77.455</v>
       </c>
     </row>
     <row r="101">
@@ -12822,7 +12822,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E163" s="5" t="n">
         <v>20.435</v>
       </c>
@@ -12863,7 +12867,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">

--- a/output/pdf_financials_xlsx/SIA.xlsx
+++ b/output/pdf_financials_xlsx/SIA.xlsx
@@ -3923,25 +3923,25 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-2.204</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.448</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-2.608</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-2.612</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-2.4</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-3.082</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-1.861</v>
       </c>
     </row>
     <row r="117">
@@ -12947,7 +12947,11 @@
           <t>Deferred income tax recoveries</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -13586,7 +13590,11 @@
           <t>Purchase of intangible assets 10</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -14662,7 +14670,11 @@
           <t>Purchase of intangible assets 9</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E203" s="5" t="n">
         <v>-2.204</v>
       </c>
